--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45A2C453-E877-4DBC-BC42-D21178ED04DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA52D15A-737F-4714-836A-222CA35B9739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="26">
-  <si>
-    <t>Type</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
   <si>
     <t>Id</t>
   </si>
@@ -41,9 +38,6 @@
   </si>
   <si>
     <t>Extra</t>
-  </si>
-  <si>
-    <t>Model</t>
   </si>
   <si>
     <t>COMPONENT_TYPE_MODEL_PLAYER</t>
@@ -1049,10 +1043,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="37.75" customWidth="1"/>
+    <col min="2" max="2" width="39" customWidth="1"/>
+    <col min="3" max="3" width="34.5" customWidth="1"/>
+    <col min="5" max="5" width="43.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1071,168 +1071,141 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="D2">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
+      <c r="D9" t="s">
+        <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA52D15A-737F-4714-836A-222CA35B9739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C82E56-6078-4FF8-B19E-6C50E7BD8295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>

--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C82E56-6078-4FF8-B19E-6C50E7BD8295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6886DB86-94BF-41AA-8AFA-4CEE77061E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
   <si>
     <t>Id</t>
   </si>
@@ -92,6 +92,18 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Models/Custom/Headgear/Man_Cap1.meshbin</t>
+  </si>
+  <si>
+    <t>Model_BigSword</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Weapon/BigSword/BigSword.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaticMesh</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1043,12 +1055,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.75" customWidth="1"/>
-    <col min="2" max="2" width="39" customWidth="1"/>
+    <col min="2" max="2" width="72.25" customWidth="1"/>
     <col min="3" max="3" width="34.5" customWidth="1"/>
+    <col min="4" max="4" width="18.625" customWidth="1"/>
     <col min="5" max="5" width="43.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1208,6 +1221,23 @@
         <v>9</v>
       </c>
     </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6886DB86-94BF-41AA-8AFA-4CEE77061E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EAFEDBE-ECAF-4731-B7A3-35CFCE1FA25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="5895" yWindow="1815" windowWidth="21600" windowHeight="11295" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelTable" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
   <si>
     <t>Id</t>
   </si>
@@ -38,12 +38,6 @@
   </si>
   <si>
     <t>Extra</t>
-  </si>
-  <si>
-    <t>COMPONENT_TYPE_MODEL_PLAYER</t>
-  </si>
-  <si>
-    <t>../../Client/Bin/Resources/Models/Gaara/SK_CHR_Gaara.meshbin</t>
   </si>
   <si>
     <t>SkeletalMesh</t>
@@ -1055,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.75" customWidth="1"/>
@@ -1087,19 +1081,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1113,10 +1107,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1130,10 +1124,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1147,10 +1141,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1164,10 +1158,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1181,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1198,10 +1192,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1215,27 +1209,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EAFEDBE-ECAF-4731-B7A3-35CFCE1FA25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A527B61-3AE6-432E-9249-949596AF60F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5895" yWindow="1815" windowWidth="21600" windowHeight="11295" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelTable" sheetId="1" r:id="rId1"/>
@@ -55,13 +55,7 @@
     <t>COMPONENT_TYPE_MODEL_SASKE</t>
   </si>
   <si>
-    <t>../../Client/Bin/Resources/Models/Saske/Saske.meshbin</t>
-  </si>
-  <si>
     <t>Model_TestModel</t>
-  </si>
-  <si>
-    <t>../../Client/Bin/Resources/Models/Custom/Animation/TesetNormal.meshbin</t>
   </si>
   <si>
     <t>Model_Body_Upper_Armor1</t>
@@ -97,6 +91,14 @@
   </si>
   <si>
     <t>StaticMesh</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Saske/Saske.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Animation/Custom.meshbin</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1101,7 +1103,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1115,10 +1117,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1132,10 +1134,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1149,10 +1151,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1166,10 +1168,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1183,10 +1185,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1200,16 +1202,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>

--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A527B61-3AE6-432E-9249-949596AF60F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99E11B40-027D-4D2C-B256-6CF74CE70B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>

--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99E11B40-027D-4D2C-B256-6CF74CE70B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE9564B-6411-4E7C-A5AB-18268E4A9675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
@@ -49,9 +49,6 @@
     <t>COMPONENT_TYPE_MODEL_MONSTER</t>
   </si>
   <si>
-    <t>../../Client/Bin/Resources/Models/Boruto/Boruto.meshbin</t>
-  </si>
-  <si>
     <t>COMPONENT_TYPE_MODEL_SASKE</t>
   </si>
   <si>
@@ -99,6 +96,10 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Models/Custom/Animation/Custom.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/WhiteZetsu/WhiteZetsu.meshbin</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1086,7 +1087,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1100,10 +1101,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1117,10 +1118,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1134,10 +1135,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1151,10 +1152,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1168,10 +1169,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
         <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1185,10 +1186,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
         <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1202,16 +1203,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
         <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>

--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -5,22 +5,23 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE9564B-6411-4E7C-A5AB-18268E4A9675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C82988-5C9B-44B1-B1AB-7491A418CCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelTable" sheetId="1" r:id="rId1"/>
+    <sheet name="Skill" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="32">
   <si>
     <t>Id</t>
   </si>
@@ -100,6 +101,34 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Models/WhiteZetsu/WhiteZetsu.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rasengan_A</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Static</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/Rasengan/Meshes/SM_WEP_Eff_Rasengan_A.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rasengan_C</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rasengan_E</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/Rasengan/Meshes/SM_WEP_Eff_Rasengan_C_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/Rasengan/Meshes/SM_WEP_Eff_Rasengan_E_01.meshbin</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1222,4 +1251,91 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD49D373-093A-42F7-A9DE-6C6E78CDC1B2}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.75" customWidth="1"/>
+    <col min="2" max="2" width="79.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C82988-5C9B-44B1-B1AB-7491A418CCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE5C3A3-AFBB-480E-ADCB-EBBD21D980E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelTable" sheetId="1" r:id="rId1"/>
     <sheet name="Skill" sheetId="2" r:id="rId2"/>
+    <sheet name="ETC" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="78">
   <si>
     <t>Id</t>
   </si>
@@ -129,6 +130,190 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Skills/Rasengan/Meshes/SM_WEP_Eff_Rasengan_E_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RasenShuriken_01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RasenShuriken_02</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RasenShuriken_03</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RasenShuriken_04</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/RasenShuriken/Meshes/SM_WEP_Eff_TrueRasenShuriken_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/RasenShuriken/Meshes/SM_WEP_Eff_TrueRasenShuriken_02.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/RasenShuriken/Meshes/SM_WEP_Eff_TrueRasenShuriken_03.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/RasenShuriken/Meshes/SM_WEP_Eff_TrueRasenShuriken_04.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chidori</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/Chidori/Meshes/Chidori.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>FireBall_A</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>FireBall_B</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>FireBall_D</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/FireBall/Meshes/FireBall_A.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/FireBall/Meshes/FireBall_B.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/FireBall/Meshes/FireBall_D.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Circle_01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Circle_02</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Claw_A</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring_01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring_02</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring_05</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring_06</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring_07</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Smoke_02</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sphere_02</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sphere_A_01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring_08</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Smoke_01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SmokeRing_01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stone_E_1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/ETC/Meshes/Stone/Stone_E_1.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/ETC/Meshes/Smoke/Smoke_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/ETC/Meshes/Smoke/SmokeRing_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/ETC/Meshes/Common/Circle_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/ETC/Meshes/Common/Circle_02.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/ETC/Meshes/Common/Claw_A_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/ETC/Meshes/Common/Ring_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/ETC/Meshes/Common/Ring_02.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/ETC/Meshes/Common/Ring_05.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/ETC/Meshes/Common/Ring_06.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/ETC/Meshes/Common/Ring_07.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/ETC/Meshes/Common/Ring_08.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/ETC/Meshes/Common/Smoke_02.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/ETC/Meshes/Common/Sphere_02.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Skills/ETC/Meshes/Common/Sphere_A_01.meshbin</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1255,10 +1440,233 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD49D373-093A-42F7-A9DE-6C6E78CDC1B2}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
+    <col min="2" max="2" width="94.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F0E888-FC6C-4A32-AA60-9E71DA63FDBE}">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="79.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1285,10 +1693,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1302,10 +1710,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1319,10 +1727,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1331,6 +1739,210 @@
         <v>21</v>
       </c>
       <c r="E4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" t="s">
         <v>26</v>
       </c>
     </row>

--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -8,21 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE5C3A3-AFBB-480E-ADCB-EBBD21D980E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC5E98B-2615-4FA9-AF66-39F16DADCCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelTable" sheetId="1" r:id="rId1"/>
-    <sheet name="Skill" sheetId="2" r:id="rId2"/>
-    <sheet name="ETC" sheetId="3" r:id="rId3"/>
+    <sheet name="Headgear" sheetId="4" r:id="rId2"/>
+    <sheet name="Onepiece" sheetId="5" r:id="rId3"/>
+    <sheet name="Skill" sheetId="2" r:id="rId4"/>
+    <sheet name="ETC" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="94">
   <si>
     <t>Id</t>
   </si>
@@ -57,18 +59,6 @@
     <t>Model_TestModel</t>
   </si>
   <si>
-    <t>Model_Body_Upper_Armor1</t>
-  </si>
-  <si>
-    <t>../../Client/Bin/Resources/Models/Custom/Body_Upper/Armor1.meshbin</t>
-  </si>
-  <si>
-    <t>Model_Body_Upper_Coat15</t>
-  </si>
-  <si>
-    <t>../../Client/Bin/Resources/Models/Custom/Body_Upper/Coat15.meshbin</t>
-  </si>
-  <si>
     <t>Model_Face_Face1</t>
   </si>
   <si>
@@ -314,6 +304,86 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Skills/ETC/Meshes/Common/Sphere_A_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_AllBack</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Headgear/Man_AllBack_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/OnePiece/Armor1.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/OnePiece/Coat15.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_OnePiece_Armor1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_OnePiece_Coat15</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_OnePiece_Armor2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_OnePiece_Armor3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_OnePiece_Minato</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/OnePiece/Minato.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/OnePiece/Armor3.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/OnePiece/Armor2.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_ManHat_03</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_SnowHead</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_PajamaHat</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Umbrella</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Headgear/Man_Hat_03.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Headgear/Man_PajamaHat.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Headgear/Man_SnowHead.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Headgear/Man_Umbrella.meshbin</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1266,14 +1336,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.75" customWidth="1"/>
     <col min="2" max="2" width="72.25" customWidth="1"/>
-    <col min="3" max="3" width="34.5" customWidth="1"/>
+    <col min="3" max="3" width="6.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.625" customWidth="1"/>
-    <col min="5" max="5" width="43.5" customWidth="1"/>
+    <col min="5" max="5" width="6.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -1301,7 +1371,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1318,7 +1388,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1335,7 +1405,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1366,69 +1436,18 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1439,6 +1458,265 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE10A3A-992E-42A2-AB63-E3DD5858D3EA}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="73.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A563EB18-FB0F-438F-86E3-42B2DF845850}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD49D373-093A-42F7-A9DE-6C6E78CDC1B2}">
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1470,189 +1748,189 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
         <v>32</v>
       </c>
-      <c r="B5" t="s">
-        <v>36</v>
-      </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
-        <v>37</v>
-      </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
         <v>34</v>
       </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
         <v>35</v>
       </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1661,7 +1939,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F0E888-FC6C-4A32-AA60-9E71DA63FDBE}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1693,257 +1971,257 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
         <v>60</v>
       </c>
-      <c r="B14" t="s">
-        <v>64</v>
-      </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
         <v>61</v>
       </c>
-      <c r="B15" t="s">
-        <v>65</v>
-      </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC5E98B-2615-4FA9-AF66-39F16DADCCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07B736E-0394-467E-94F4-36B53B4DB919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelTable" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="96">
   <si>
     <t>Id</t>
   </si>
@@ -384,6 +384,14 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Models/Custom/Headgear/Man_Umbrella.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Samehada</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Weapon/Samehada/Samehada.meshbin</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1336,7 +1344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.75" customWidth="1"/>
@@ -1448,6 +1456,23 @@
         <v>17</v>
       </c>
       <c r="E6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07B736E-0394-467E-94F4-36B53B4DB919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DC70F1-3293-454A-AC99-15DB648738A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelTable" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="104">
   <si>
     <t>Id</t>
   </si>
@@ -392,6 +392,38 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Models/Weapon/Samehada/Samehada.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sky_SkySphere_Base</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sky_CloudPlate_01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/SkySphere/CloudPlate_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/SkySphere/SkySphere.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sky_SkySphere_01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/SkySphere/SkySphere_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sky_Cloudy</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/SkySphere/SkySphere_cloudy.meshbin</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1966,10 +1998,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F0E888-FC6C-4A32-AA60-9E71DA63FDBE}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.75" customWidth="1"/>
     <col min="2" max="2" width="79.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.125" bestFit="1" customWidth="1"/>
   </cols>
@@ -2249,6 +2281,74 @@
         <v>22</v>
       </c>
     </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DC70F1-3293-454A-AC99-15DB648738A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666512B7-F484-4AC8-88C4-1FA4B1A196B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelTable" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="106">
   <si>
     <t>Id</t>
   </si>
@@ -424,6 +424,14 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Models/SkySphere/SkySphere_cloudy.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Shuriken</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/WindmilShuriken/WindmilShuriken.meshbin</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1376,14 +1384,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.75" customWidth="1"/>
     <col min="2" max="2" width="72.25" customWidth="1"/>
     <col min="3" max="3" width="6.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.625" customWidth="1"/>
-    <col min="5" max="5" width="6.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -1506,6 +1514,23 @@
       </c>
       <c r="E7" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666512B7-F484-4AC8-88C4-1FA4B1A196B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0085C32-46E9-4656-A162-8D9B394311A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelTable" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="117">
   <si>
     <t>Id</t>
   </si>
@@ -432,6 +432,50 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Models/WindmilShuriken/WindmilShuriken.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShinsuSenju</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kirin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/ShinsuSenju/ShinsuSenju.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkeletalMesh</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShinsuSenju_Arm</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/ShinsuSenju/ShinsuSenju_Arm.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Kirin/Kirin.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Replacement</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Replacement/Replacement_Tree.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Replacement_Text</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Replacement/Replacement_Text.meshbin</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1384,7 +1428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.75" customWidth="1"/>
@@ -1530,6 +1574,40 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1800,12 +1878,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD49D373-093A-42F7-A9DE-6C6E78CDC1B2}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
     <col min="2" max="2" width="94.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -2012,6 +2090,57 @@
         <v>17</v>
       </c>
       <c r="E12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" t="s">
         <v>22</v>
       </c>
     </row>

--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0085C32-46E9-4656-A162-8D9B394311A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897C0A50-21A3-4CB0-9897-00837C525C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelTable" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="139">
   <si>
     <t>Id</t>
   </si>
@@ -476,6 +476,87 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Models/Replacement/Replacement_Text.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuardBreak_A</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuardBreak_C</t>
+  </si>
+  <si>
+    <t>Rock_2</t>
+  </si>
+  <si>
+    <t>SmallRock_01</t>
+  </si>
+  <si>
+    <t>Stone_01</t>
+  </si>
+  <si>
+    <t>Stone_02</t>
+  </si>
+  <si>
+    <t>Stone_03</t>
+  </si>
+  <si>
+    <t>Stone_04</t>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Earth/GuardBreak_A.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuardBreak_B</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Earth/GuardBreak_B.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Earth/GuardBreak_C.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Earth/Rock_2.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Earth/SmallRock_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Earth/Stone_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Earth/Stone_02.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Earth/Stone_03.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Earth/Stone_04.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShinsuSenju_Arm_Long</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/ShinsuSenju/ShinsuSenju_Arm_Long.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Pain</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Pain/Pain.meshbin</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1428,7 +1509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.75" customWidth="1"/>
@@ -1608,6 +1689,23 @@
         <v>17</v>
       </c>
       <c r="E10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1878,7 +1976,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD49D373-093A-42F7-A9DE-6C6E78CDC1B2}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
@@ -2144,6 +2242,23 @@
         <v>22</v>
       </c>
     </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2152,7 +2267,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F0E888-FC6C-4A32-AA60-9E71DA63FDBE}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.75" customWidth="1"/>
@@ -2503,6 +2618,159 @@
         <v>22</v>
       </c>
     </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B26" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897C0A50-21A3-4CB0-9897-00837C525C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0FB765-5FA0-4A41-B56F-F0B3686A84E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelTable" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="171">
   <si>
     <t>Id</t>
   </si>
@@ -557,6 +557,134 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Models/Pain/Pain.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stone_Stone_01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stone_Stone_02</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stone_Stone_03</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stone_Stone_04</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Earth/Stone_Stone_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Earth/Stone_Stone_02.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Earth/Stone_Stone_03.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Earth/Stone_Stone_04.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Planet</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Earth/PlanetaryDevastation_A_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SandShower_04</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Kirin/SandShower_04.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line_A_01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Line/Line_A_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line_A_02</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line_A_03</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line_A_04</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line_A_05</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line_A_06</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Line/Line_A_02.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Line/Line_A_03.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Line/Line_A_04.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Line/Line_A_05.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Line/Line_A_06.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>AirRibbon_01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/AirRibbon/AirRibbon_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>AirRibbon_02</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>AirRibbon_03</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/AirRibbon/AirRibbon_02.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/AirRibbon/AirRibbon_03.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wire</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Wire/Wire.meshbin</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1976,7 +2104,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD49D373-093A-42F7-A9DE-6C6E78CDC1B2}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
@@ -2259,6 +2387,176 @@
         <v>22</v>
       </c>
     </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>154</v>
+      </c>
+      <c r="B20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>155</v>
+      </c>
+      <c r="B21" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>157</v>
+      </c>
+      <c r="B23" t="s">
+        <v>162</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B24" t="s">
+        <v>164</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>165</v>
+      </c>
+      <c r="B25" t="s">
+        <v>167</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>166</v>
+      </c>
+      <c r="B26" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2267,7 +2565,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F0E888-FC6C-4A32-AA60-9E71DA63FDBE}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.75" customWidth="1"/>
@@ -2771,6 +3069,108 @@
         <v>22</v>
       </c>
     </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>139</v>
+      </c>
+      <c r="B30" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>140</v>
+      </c>
+      <c r="B31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>141</v>
+      </c>
+      <c r="B32" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B33" t="s">
+        <v>146</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>147</v>
+      </c>
+      <c r="B34" t="s">
+        <v>148</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>169</v>
+      </c>
+      <c r="B35" t="s">
+        <v>170</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0FB765-5FA0-4A41-B56F-F0B3686A84E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA1D778-613D-406D-8408-91B53F598DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelTable" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="175">
   <si>
     <t>Id</t>
   </si>
@@ -685,6 +685,22 @@
   </si>
   <si>
     <t>../../Client/Bin/Resources/Models/Wire/Wire.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>WoodHand_L</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>WoodHand_R</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/WoodHand/WoodHand_R.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/WoodHand/WoodHand_L.meshbin</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2104,7 +2120,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD49D373-093A-42F7-A9DE-6C6E78CDC1B2}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
@@ -2554,6 +2570,40 @@
         <v>17</v>
       </c>
       <c r="E26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" t="s">
+        <v>173</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" t="s">
         <v>22</v>
       </c>
     </row>

--- a/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Model.xlsx
@@ -8,23 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA1D778-613D-406D-8408-91B53F598DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F798075F-7D37-4C05-B576-D977C8616969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelTable" sheetId="1" r:id="rId1"/>
-    <sheet name="Headgear" sheetId="4" r:id="rId2"/>
-    <sheet name="Onepiece" sheetId="5" r:id="rId3"/>
-    <sheet name="Skill" sheetId="2" r:id="rId4"/>
-    <sheet name="ETC" sheetId="3" r:id="rId5"/>
+    <sheet name="Face" sheetId="6" r:id="rId2"/>
+    <sheet name="Upper" sheetId="7" r:id="rId3"/>
+    <sheet name="Lower" sheetId="8" r:id="rId4"/>
+    <sheet name="Headgear" sheetId="4" r:id="rId5"/>
+    <sheet name="Onepiece" sheetId="5" r:id="rId6"/>
+    <sheet name="Skill" sheetId="2" r:id="rId7"/>
+    <sheet name="ETC" sheetId="3" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="200">
   <si>
     <t>Id</t>
   </si>
@@ -65,12 +68,6 @@
     <t>../../Client/Bin/Resources/Models/Custom/Face/Face1.meshbin</t>
   </si>
   <si>
-    <t>Model_Headgear_Man_Cap1</t>
-  </si>
-  <si>
-    <t>../../Client/Bin/Resources/Models/Custom/Headgear/Man_Cap1.meshbin</t>
-  </si>
-  <si>
     <t>Model_BigSword</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -307,30 +304,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Model_AllBack</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>../../Client/Bin/Resources/Models/Custom/Headgear/Man_AllBack_01.meshbin</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>../../Client/Bin/Resources/Models/Custom/OnePiece/Armor1.meshbin</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>../../Client/Bin/Resources/Models/Custom/OnePiece/Coat15.meshbin</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Model_OnePiece_Armor1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Model_OnePiece_Coat15</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Model_OnePiece_Armor2</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -439,10 +412,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Kirin</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>../../Client/Bin/Resources/Models/ShinsuSenju/ShinsuSenju.meshbin</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -459,10 +428,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>../../Client/Bin/Resources/Models/Kirin/Kirin.meshbin</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Model_Replacement</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -600,14 +565,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>SandShower_04</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>../../Client/Bin/Resources/Models/Kirin/SandShower_04.meshbin</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Line_A_01</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -702,6 +659,150 @@
   <si>
     <t>../../Client/Bin/Resources/Models/WoodHand/WoodHand_L.meshbin</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Face_Mask1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Face_Mask2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Face/Face_Mask1.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Face/Face_Mask2.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Body_Upper/Haori_01.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Upper_Jiraiya</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Upper_LeatherJaket</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Upper_Logo</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Upper_Sai</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Upper_Saske</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Body_Upper/Upper_LeatherJaket.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Body_Upper/Upper_Logo.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Body_Upper/Upper_Sai.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Body_Upper/Upper_Saske.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Lower_LeatherPants</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Lower_Lower_PantsCut</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Lower_Lower_StonePants</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_Lower_Lower_Trainer</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Body_Lower/Lower_LeatherPants.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Body_Lower/Lower_PantsCut.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Body_Lower/Lower_StonePants.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Body_Lower/Lower_Trainer.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_FrogHead</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Headgear/Frog_Head.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_MadaraHead</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/Headgear/Madara_Head.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_OnePiece_Akachiki</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_OnePiece_Frog</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/OnePiece/Akachiki_Coat.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/OnePiece/Frogs.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_OnePiece_Jaket</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/Custom/OnePiece/Onepiece_Jaket.meshbin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model_BoxingGlove_Left</t>
+  </si>
+  <si>
+    <t>Model_BoxingGlove_Right</t>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/BoxingGloves/BoxingGloves_L.meshbin</t>
+  </si>
+  <si>
+    <t>../../Client/Bin/Resources/Models/BoxingGloves/BoxingGloves_R.meshbin</t>
   </si>
 </sst>
 </file>
@@ -1653,7 +1754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.75" customWidth="1"/>
@@ -1665,7 +1766,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1688,7 +1789,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1705,7 +1806,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1722,7 +1823,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1736,16 +1837,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -1753,16 +1854,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -1770,87 +1871,70 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" t="s">
         <v>104</v>
       </c>
-      <c r="B8" t="s">
-        <v>105</v>
-      </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>137</v>
-      </c>
-      <c r="B11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1860,6 +1944,320 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{795EEC2D-F687-42C5-9DA8-3B3978D9EA35}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B29C01-D800-4C00-B813-327983BEC5A0}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="79" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D28E9A0-BB4C-43C2-B550-112DBC5BE573}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="78.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE10A3A-992E-42A2-AB63-E3DD5858D3EA}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1891,10 +2289,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1903,92 +2301,92 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>186</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>187</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>188</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>189</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1997,9 +2395,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A563EB18-FB0F-438F-86E3-42B2DF845850}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.625" bestFit="1" customWidth="1"/>
@@ -2029,10 +2427,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2046,10 +2444,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -2063,10 +2461,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2080,10 +2478,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>190</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2097,10 +2495,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>191</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2109,6 +2507,23 @@
         <v>6</v>
       </c>
       <c r="E6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2118,9 +2533,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD49D373-093A-42F7-A9DE-6C6E78CDC1B2}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
@@ -2150,461 +2565,427 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B16" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B17" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B19" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B20" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B22" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B23" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="E25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="E26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>171</v>
-      </c>
-      <c r="B27" t="s">
-        <v>174</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27" t="s">
-        <v>109</v>
-      </c>
-      <c r="E27" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>172</v>
-      </c>
-      <c r="B28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28" t="s">
-        <v>109</v>
-      </c>
-      <c r="E28" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2613,12 +2994,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F0E888-FC6C-4A32-AA60-9E71DA63FDBE}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.75" customWidth="1"/>
+    <col min="1" max="1" width="23.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="79.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.125" bestFit="1" customWidth="1"/>
   </cols>
@@ -2645,580 +3026,614 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B21" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B22" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" t="s">
         <v>118</v>
       </c>
-      <c r="B23" t="s">
-        <v>128</v>
-      </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" t="s">
         <v>119</v>
       </c>
-      <c r="B24" t="s">
-        <v>129</v>
-      </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" t="s">
         <v>120</v>
       </c>
-      <c r="B25" t="s">
-        <v>130</v>
-      </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" t="s">
         <v>121</v>
       </c>
-      <c r="B26" t="s">
-        <v>131</v>
-      </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" t="s">
         <v>122</v>
       </c>
-      <c r="B27" t="s">
-        <v>132</v>
-      </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" t="s">
         <v>123</v>
       </c>
-      <c r="B28" t="s">
-        <v>133</v>
-      </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" t="s">
         <v>124</v>
       </c>
-      <c r="B29" t="s">
-        <v>134</v>
-      </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B30" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E30" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B31" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B32" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B33" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E33" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="B34" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="B35" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>22</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>196</v>
+      </c>
+      <c r="B36" t="s">
+        <v>198</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>197</v>
+      </c>
+      <c r="B37" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
